--- a/catalog_test_50.xlsx
+++ b/catalog_test_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="189">
   <si>
     <t>name</t>
   </si>
@@ -560,6 +560,27 @@
   </si>
   <si>
     <t>https://picsum.photos/seed/thermal/600/400</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>обувь</t>
+  </si>
+  <si>
+    <t>штаны</t>
+  </si>
+  <si>
+    <t>аксессуары</t>
+  </si>
+  <si>
+    <t>верхняя одежда</t>
+  </si>
+  <si>
+    <t>футболки</t>
+  </si>
+  <si>
+    <t>рубашки</t>
   </si>
 </sst>
 </file>
@@ -907,12 +928,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.5703125" customWidth="1"/>
     <col min="2" max="2" width="66.140625" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="71" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
     <col min="6" max="6" width="32.42578125" customWidth="1"/>
@@ -920,7 +941,7 @@
     <col min="8" max="8" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -933,8 +954,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -947,8 +971,11 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -961,8 +988,11 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -975,8 +1005,11 @@
       <c r="D4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -989,8 +1022,11 @@
       <c r="D5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1003,8 +1039,11 @@
       <c r="D6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1017,8 +1056,11 @@
       <c r="D7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1031,8 +1073,11 @@
       <c r="D8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1045,8 +1090,11 @@
       <c r="D9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1059,8 +1107,11 @@
       <c r="D10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -1073,8 +1124,11 @@
       <c r="D11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1087,8 +1141,11 @@
       <c r="D12" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1101,8 +1158,11 @@
       <c r="D13" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1115,8 +1175,11 @@
       <c r="D14" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1129,8 +1192,11 @@
       <c r="D15" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -1143,8 +1209,11 @@
       <c r="D16" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1157,8 +1226,11 @@
       <c r="D17" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -1171,8 +1243,11 @@
       <c r="D18" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -1185,8 +1260,11 @@
       <c r="D19" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -1199,8 +1277,11 @@
       <c r="D20" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -1213,8 +1294,11 @@
       <c r="D21" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -1227,8 +1311,11 @@
       <c r="D22" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -1241,8 +1328,11 @@
       <c r="D23" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -1255,8 +1345,11 @@
       <c r="D24" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -1269,8 +1362,11 @@
       <c r="D25" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -1283,8 +1379,11 @@
       <c r="D26" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -1297,8 +1396,11 @@
       <c r="D27" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -1311,8 +1413,11 @@
       <c r="D28" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>84</v>
       </c>
@@ -1325,8 +1430,11 @@
       <c r="D29" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -1339,8 +1447,11 @@
       <c r="D30" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -1353,8 +1464,11 @@
       <c r="D31" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>93</v>
       </c>
@@ -1367,8 +1481,11 @@
       <c r="D32" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -1381,8 +1498,11 @@
       <c r="D33" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -1395,8 +1515,11 @@
       <c r="D34" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>102</v>
       </c>
@@ -1409,8 +1532,11 @@
       <c r="D35" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>105</v>
       </c>
@@ -1423,8 +1549,11 @@
       <c r="D36" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>108</v>
       </c>
@@ -1437,8 +1566,11 @@
       <c r="D37" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>111</v>
       </c>
@@ -1451,8 +1583,11 @@
       <c r="D38" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>114</v>
       </c>
@@ -1465,8 +1600,11 @@
       <c r="D39" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>117</v>
       </c>
@@ -1479,8 +1617,11 @@
       <c r="D40" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -1493,8 +1634,11 @@
       <c r="D41" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -1507,8 +1651,11 @@
       <c r="D42" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -1521,8 +1668,11 @@
       <c r="D43" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -1535,8 +1685,11 @@
       <c r="D44" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>132</v>
       </c>
@@ -1549,8 +1702,11 @@
       <c r="D45" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>135</v>
       </c>
@@ -1563,8 +1719,11 @@
       <c r="D46" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>138</v>
       </c>
@@ -1577,8 +1736,11 @@
       <c r="D47" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>141</v>
       </c>
@@ -1591,8 +1753,11 @@
       <c r="D48" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -1605,8 +1770,11 @@
       <c r="D49" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>147</v>
       </c>
@@ -1619,8 +1787,11 @@
       <c r="D50" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>120</v>
       </c>
@@ -1633,8 +1804,11 @@
       <c r="D51" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>152</v>
       </c>
@@ -1647,8 +1821,11 @@
       <c r="D52" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>153</v>
       </c>
@@ -1661,8 +1838,11 @@
       <c r="D53" s="1" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>156</v>
       </c>
@@ -1675,8 +1855,11 @@
       <c r="D54" s="1" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>157</v>
       </c>
@@ -1689,8 +1872,11 @@
       <c r="D55" s="1" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>158</v>
       </c>
@@ -1703,8 +1889,11 @@
       <c r="D56" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>159</v>
       </c>
@@ -1717,8 +1906,11 @@
       <c r="D57" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>160</v>
       </c>
@@ -1731,8 +1923,11 @@
       <c r="D58" s="1" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>161</v>
       </c>
@@ -1745,8 +1940,11 @@
       <c r="D59" s="1" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>162</v>
       </c>
@@ -1759,8 +1957,11 @@
       <c r="D60" s="1" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>163</v>
       </c>
@@ -1772,6 +1973,9 @@
       </c>
       <c r="D61" s="1" t="s">
         <v>181</v>
+      </c>
+      <c r="E61" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
